--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488276_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488276_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.605</v>
+        <v>6.9612</v>
       </c>
       <c r="E2" t="n">
-        <v>7.2745</v>
+        <v>7.286</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.6696</v>
+        <v>-0.3249</v>
       </c>
       <c r="G2" t="n">
         <v>6.1706</v>
@@ -610,13 +610,13 @@
         <v>2.0382</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.7302</v>
+        <v>-0.374</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2873</v>
+        <v>0.2988</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.0175</v>
+        <v>-0.6728</v>
       </c>
       <c r="V2" t="n">
         <v>2.8321</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.1485</v>
+        <v>3.9625</v>
       </c>
       <c r="E3" t="n">
-        <v>4.2695</v>
+        <v>4.3789</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.121</v>
+        <v>-0.4164</v>
       </c>
       <c r="G3" t="n">
         <v>3.1733</v>
@@ -688,13 +688,13 @@
         <v>1.297</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.008</v>
+        <v>-0.194</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1131</v>
+        <v>-0.0037</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1052</v>
+        <v>-0.1903</v>
       </c>
       <c r="V3" t="n">
         <v>-0.3139</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>L. RAMOS CASTRO</t>
+          <t>J. SANCHEZ BARQUIN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.1742</v>
+        <v>2.6892</v>
       </c>
       <c r="E4" t="n">
-        <v>2.5867</v>
+        <v>3.5181</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5875</v>
+        <v>-0.8289</v>
       </c>
       <c r="G4" t="n">
-        <v>2.1729</v>
+        <v>2.228</v>
       </c>
       <c r="H4" t="n">
-        <v>3.4708</v>
+        <v>0.3158</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.2979</v>
+        <v>1.9122</v>
       </c>
       <c r="J4" t="n">
-        <v>3.681</v>
+        <v>3.3816</v>
       </c>
       <c r="K4" t="n">
-        <v>4.7794</v>
+        <v>1.2239</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.0984</v>
+        <v>2.1578</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.5081</v>
+        <v>-1.1537</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.3085</v>
+        <v>-0.9081</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.1996</v>
+        <v>-0.2456</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5558999999999999</v>
+        <v>1.4823</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>1.4823</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4454</v>
+        <v>-0.7066</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1679</v>
+        <v>0.1365</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6133</v>
+        <v>-0.8431</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-0.3144</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. KVERNADZE</t>
+          <t>L. RAMOS CASTRO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.927</v>
+        <v>2.3694</v>
       </c>
       <c r="E5" t="n">
-        <v>1.8625</v>
+        <v>2.2497</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0645</v>
+        <v>0.1197</v>
       </c>
       <c r="G5" t="n">
-        <v>1.4194</v>
+        <v>2.1729</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1753</v>
+        <v>3.4708</v>
       </c>
       <c r="I5" t="n">
-        <v>1.2441</v>
+        <v>-1.2979</v>
       </c>
       <c r="J5" t="n">
-        <v>1.9528</v>
+        <v>3.681</v>
       </c>
       <c r="K5" t="n">
-        <v>1.1849</v>
+        <v>4.7794</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7678</v>
+        <v>-1.0984</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5334</v>
+        <v>-1.5081</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.0097</v>
+        <v>-1.3085</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4763</v>
+        <v>-0.1996</v>
       </c>
       <c r="P5" t="n">
-        <v>1.6676</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R5" t="n">
-        <v>1.6676</v>
+        <v>1.4823</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.53</v>
+        <v>-0.3594</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5397</v>
+        <v>-0.5049</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.0697</v>
+        <v>0.1455</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.63</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.63</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. SANCHEZ BARQUIN</t>
+          <t>S. KVERNADZE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2059</v>
+        <v>1.8116</v>
       </c>
       <c r="E6" t="n">
-        <v>2.5273</v>
+        <v>1.5255</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.3214</v>
+        <v>0.2861</v>
       </c>
       <c r="G6" t="n">
-        <v>2.228</v>
+        <v>1.4194</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3158</v>
+        <v>0.1753</v>
       </c>
       <c r="I6" t="n">
-        <v>1.9122</v>
+        <v>1.2441</v>
       </c>
       <c r="J6" t="n">
-        <v>3.3816</v>
+        <v>1.9528</v>
       </c>
       <c r="K6" t="n">
-        <v>1.2239</v>
+        <v>1.1849</v>
       </c>
       <c r="L6" t="n">
-        <v>2.1578</v>
+        <v>0.7678</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.1537</v>
+        <v>-0.5334</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.9081</v>
+        <v>-1.0097</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2456</v>
+        <v>0.4763</v>
       </c>
       <c r="P6" t="n">
-        <v>1.4823</v>
+        <v>1.6676</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.4823</v>
+        <v>1.6676</v>
       </c>
       <c r="S6" t="n">
-        <v>-2.1899</v>
+        <v>-0.6454</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8542999999999999</v>
+        <v>0.2027</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.3356</v>
+        <v>-0.8481</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.3144</v>
+        <v>-0.63</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>-0.63</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.3144</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. KALLE</t>
+          <t>S. CISSE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1234</v>
+        <v>-0.9891</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1842</v>
+        <v>-0.5524</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0608</v>
+        <v>-0.4366</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.6163999999999999</v>
+        <v>0.9409</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.4676</v>
+        <v>-0.2449</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8512</v>
+        <v>1.1858</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7285</v>
+        <v>2.0279</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.3912</v>
+        <v>-0.0564</v>
       </c>
       <c r="L8" t="n">
-        <v>1.1197</v>
+        <v>2.0842</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.3449</v>
+        <v>-1.087</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.0764</v>
+        <v>-0.1885</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2686</v>
+        <v>-0.8984</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.1853</v>
+        <v>-2.0382</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.8529</v>
+        <v>-3.7057</v>
       </c>
       <c r="R8" t="n">
         <v>1.6676</v>
       </c>
       <c r="S8" t="n">
-        <v>1.3077</v>
+        <v>0.1082</v>
       </c>
       <c r="T8" t="n">
-        <v>0.9401</v>
+        <v>0.1816</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3675</v>
+        <v>-0.07340000000000001</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.6294</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.9439</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.6294</v>
+        <v>-0.9439</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S. CISSE</t>
+          <t>S. KALLE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.0684</v>
+        <v>-1.1137</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.6071</v>
+        <v>-0.5097</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4613</v>
+        <v>-0.604</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9409</v>
+        <v>-0.6163999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.2449</v>
+        <v>-1.4676</v>
       </c>
       <c r="I9" t="n">
-        <v>1.1858</v>
+        <v>0.8512</v>
       </c>
       <c r="J9" t="n">
-        <v>2.0279</v>
+        <v>0.7285</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.0564</v>
+        <v>-0.3912</v>
       </c>
       <c r="L9" t="n">
-        <v>2.0842</v>
+        <v>1.1197</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.087</v>
+        <v>-1.3449</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1885</v>
+        <v>-1.0764</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.8984</v>
+        <v>-0.2686</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.0382</v>
+        <v>-0.1853</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.7057</v>
+        <v>-1.8529</v>
       </c>
       <c r="R9" t="n">
         <v>1.6676</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0288</v>
+        <v>0.3174</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1269</v>
+        <v>0.6146</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.098</v>
+        <v>-0.2972</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.6294</v>
       </c>
       <c r="W9" t="n">
-        <v>0.9439</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.9439</v>
+        <v>-0.6294</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.4909</v>
+        <v>-1.1412</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0481</v>
+        <v>0.2007</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.539</v>
+        <v>-1.342</v>
       </c>
       <c r="G10" t="n">
         <v>0.4108</v>
@@ -1234,13 +1234,13 @@
         <v>1.297</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.014</v>
+        <v>-0.6644</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5471</v>
+        <v>-0.3945</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4668</v>
+        <v>-0.2699</v>
       </c>
       <c r="V10" t="n">
         <v>-1.2583</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.1125</v>
+        <v>-3.4636</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.7172</v>
+        <v>-1.2161</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.3953</v>
+        <v>-2.2476</v>
       </c>
       <c r="G11" t="n">
         <v>-2.1002</v>
@@ -1312,13 +1312,13 @@
         <v>1.297</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.4385</v>
+        <v>-0.7896</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6901</v>
+        <v>-0.189</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.7484</v>
+        <v>-0.6006</v>
       </c>
       <c r="V11" t="n">
         <v>-0.9444</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>10.9095</v>
+        <v>11.7304</v>
       </c>
       <c r="E12" t="n">
-        <v>16.7042</v>
+        <v>17.5248</v>
       </c>
       <c r="F12" t="n">
-        <v>-5.7948</v>
+        <v>-5.7946</v>
       </c>
       <c r="G12" t="n">
         <v>14.4434</v>
@@ -1390,13 +1390,13 @@
         <v>13.8966</v>
       </c>
       <c r="S12" t="n">
-        <v>-4.1287</v>
+        <v>-3.3078</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4784999999999999</v>
+        <v>0.3420999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>-3.65</v>
+        <v>-3.6499</v>
       </c>
       <c r="V12" t="n">
         <v>-1.2583</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.7618</v>
+        <v>3.3454</v>
       </c>
       <c r="E13" t="n">
-        <v>3.5253</v>
+        <v>3.1336</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2365</v>
+        <v>0.2118</v>
       </c>
       <c r="G13" t="n">
         <v>2.7765</v>
@@ -1468,13 +1468,13 @@
         <v>0.1853</v>
       </c>
       <c r="S13" t="n">
-        <v>0.8006</v>
+        <v>0.3843</v>
       </c>
       <c r="T13" t="n">
-        <v>0.5434</v>
+        <v>0.1517</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2572</v>
+        <v>0.2325</v>
       </c>
       <c r="V13" t="n">
         <v>-0.0005</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X. NEWSON</t>
+          <t>R. SANAHUJA TRESERRAS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.2511</v>
+        <v>0.0054</v>
       </c>
       <c r="E14" t="n">
-        <v>2.7185</v>
+        <v>1.2561</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.9696</v>
+        <v>-1.2507</v>
       </c>
       <c r="G14" t="n">
-        <v>-3.0842</v>
+        <v>0.6373</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9278</v>
+        <v>-0.1276</v>
       </c>
       <c r="I14" t="n">
-        <v>-4.012</v>
+        <v>0.765</v>
       </c>
       <c r="J14" t="n">
-        <v>1.0657</v>
+        <v>2.5073</v>
       </c>
       <c r="K14" t="n">
-        <v>2.2364</v>
+        <v>0.5368000000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.1706</v>
+        <v>1.9705</v>
       </c>
       <c r="M14" t="n">
-        <v>-4.15</v>
+        <v>-1.87</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.3085</v>
+        <v>-0.6644</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.8414</v>
+        <v>-1.2056</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>-1.297</v>
       </c>
       <c r="Q14" t="n">
         <v>-1.8529</v>
       </c>
       <c r="R14" t="n">
-        <v>1.8529</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="S14" t="n">
-        <v>1.8892</v>
+        <v>0.3507</v>
       </c>
       <c r="T14" t="n">
-        <v>2.5617</v>
+        <v>0.2873</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.6725</v>
+        <v>0.0634</v>
       </c>
       <c r="V14" t="n">
-        <v>0.9439</v>
+        <v>0.3144</v>
       </c>
       <c r="W14" t="n">
-        <v>0.9439</v>
+        <v>0.3144</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R. SANAHUJA TRESERRAS</t>
+          <t>P. VILLAREJO CALATAYUD</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.2952</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8643999999999999</v>
+        <v>0.1659</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.1597</v>
+        <v>-0.234</v>
       </c>
       <c r="G15" t="n">
-        <v>0.6373</v>
+        <v>0.2105</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.1276</v>
+        <v>0.2844</v>
       </c>
       <c r="I15" t="n">
-        <v>0.765</v>
+        <v>-0.07389999999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>2.5073</v>
+        <v>2.7393</v>
       </c>
       <c r="K15" t="n">
-        <v>0.5368000000000001</v>
+        <v>2.0223</v>
       </c>
       <c r="L15" t="n">
-        <v>1.9705</v>
+        <v>0.7169</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.87</v>
+        <v>-2.5288</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.6644</v>
+        <v>-1.738</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.2056</v>
+        <v>-0.7907999999999999</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.297</v>
+        <v>-1.6676</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.8529</v>
+        <v>-3.7057</v>
       </c>
       <c r="R15" t="n">
-        <v>0.5558999999999999</v>
+        <v>2.0382</v>
       </c>
       <c r="S15" t="n">
-        <v>0.05</v>
+        <v>0.1296</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1044</v>
+        <v>-0.1265</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1544</v>
+        <v>0.2561</v>
       </c>
       <c r="V15" t="n">
-        <v>0.3144</v>
+        <v>1.2594</v>
       </c>
       <c r="W15" t="n">
-        <v>0.3144</v>
+        <v>1.2589</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>0.0005</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P. VILLAREJO CALATAYUD</t>
+          <t>A. ARCONES DURAND</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.5909</v>
+        <v>-0.7969000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.1279</v>
+        <v>3.1978</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.463</v>
+        <v>-3.9948</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2105</v>
+        <v>-2.8154</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2844</v>
+        <v>-0.6314</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.07389999999999999</v>
+        <v>-2.184</v>
       </c>
       <c r="J16" t="n">
-        <v>2.7393</v>
+        <v>3.0922</v>
       </c>
       <c r="K16" t="n">
-        <v>2.0223</v>
+        <v>1.713</v>
       </c>
       <c r="L16" t="n">
-        <v>0.7169</v>
+        <v>1.3792</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.5288</v>
+        <v>-5.9077</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.738</v>
+        <v>-2.3444</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.7907999999999999</v>
+        <v>-3.5633</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.6676</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.7057</v>
+        <v>-1.8529</v>
       </c>
       <c r="R16" t="n">
-        <v>2.0382</v>
+        <v>2.4087</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3932</v>
+        <v>0.8332000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4203</v>
+        <v>0.7000999999999999</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0271</v>
+        <v>0.133</v>
       </c>
       <c r="V16" t="n">
-        <v>1.2594</v>
+        <v>0.6294</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2589</v>
+        <v>1.2583</v>
       </c>
       <c r="X16" t="n">
-        <v>0.0005</v>
+        <v>-0.6289</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.6618</v>
+        <v>-0.9196</v>
       </c>
       <c r="E17" t="n">
-        <v>2.6081</v>
+        <v>3.2936</v>
       </c>
       <c r="F17" t="n">
-        <v>-4.2699</v>
+        <v>-4.2132</v>
       </c>
       <c r="G17" t="n">
         <v>-0.5192</v>
@@ -1780,13 +1780,13 @@
         <v>1.297</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0602</v>
+        <v>0.8024</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0261</v>
+        <v>0.7116</v>
       </c>
       <c r="U17" t="n">
-        <v>0.034</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="V17" t="n">
         <v>-1.5733</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. ARCONES DURAND</t>
+          <t>X. NEWSON</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.7035</v>
+        <v>-0.9997</v>
       </c>
       <c r="E18" t="n">
-        <v>2.4144</v>
+        <v>1.4454</v>
       </c>
       <c r="F18" t="n">
-        <v>-4.1179</v>
+        <v>-2.4451</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.8154</v>
+        <v>-3.0842</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6314</v>
+        <v>0.9278</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.184</v>
+        <v>-4.012</v>
       </c>
       <c r="J18" t="n">
-        <v>3.0922</v>
+        <v>1.0657</v>
       </c>
       <c r="K18" t="n">
-        <v>1.713</v>
+        <v>2.2364</v>
       </c>
       <c r="L18" t="n">
-        <v>1.3792</v>
+        <v>-1.1706</v>
       </c>
       <c r="M18" t="n">
-        <v>-5.9077</v>
+        <v>-4.15</v>
       </c>
       <c r="N18" t="n">
-        <v>-2.3444</v>
+        <v>-1.3085</v>
       </c>
       <c r="O18" t="n">
-        <v>-3.5633</v>
+        <v>-2.8414</v>
       </c>
       <c r="P18" t="n">
-        <v>0.5558999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>-1.8529</v>
       </c>
       <c r="R18" t="n">
-        <v>2.4087</v>
+        <v>1.8529</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.07340000000000001</v>
+        <v>1.1406</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0833</v>
+        <v>1.2886</v>
       </c>
       <c r="U18" t="n">
-        <v>0.009900000000000001</v>
+        <v>-0.148</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6294</v>
+        <v>0.9439</v>
       </c>
       <c r="W18" t="n">
-        <v>1.2583</v>
+        <v>0.9439</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.6289</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. SHANNON</t>
+          <t>R. URBANO MORENO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.1351</v>
+        <v>-2.2089</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.6126</v>
+        <v>-1.4801</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.5225</v>
+        <v>-0.7289</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.842</v>
+        <v>-2.7228</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.9051</v>
+        <v>-1.0393</v>
       </c>
       <c r="I19" t="n">
-        <v>1.0631</v>
+        <v>-1.6835</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.2033</v>
+        <v>-1.412</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.0742</v>
+        <v>-0.1892</v>
       </c>
       <c r="L19" t="n">
-        <v>0.8709</v>
+        <v>-1.2228</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.6387</v>
+        <v>-1.3108</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.8308</v>
+        <v>-0.8501</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1922</v>
+        <v>-0.4607</v>
       </c>
       <c r="P19" t="n">
-        <v>0.1853</v>
+        <v>0.3706</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1117</v>
+        <v>0.3706</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1634</v>
+        <v>0.1433</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1679</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0045</v>
+        <v>0.2114</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.315</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.315</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R. URBANO MORENO</t>
+          <t>J. SHANNON</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.6751</v>
+        <v>-2.2496</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.7739</v>
+        <v>-1.8085</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.9012</v>
+        <v>-0.4412</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.7228</v>
+        <v>-1.842</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.0393</v>
+        <v>-2.9051</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.6835</v>
+        <v>1.0631</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.412</v>
+        <v>-0.2033</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.1892</v>
+        <v>-1.0742</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.2228</v>
+        <v>0.8709</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.3108</v>
+        <v>-1.6387</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.8501</v>
+        <v>-1.8308</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.4607</v>
+        <v>0.1922</v>
       </c>
       <c r="P20" t="n">
-        <v>0.3706</v>
+        <v>0.1853</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R20" t="n">
-        <v>0.3706</v>
+        <v>1.1117</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3228</v>
+        <v>-0.2779</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3619</v>
+        <v>-0.3637</v>
       </c>
       <c r="U20" t="n">
-        <v>0.039</v>
+        <v>0.0858</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.315</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>-0.315</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.3586</v>
+        <v>-6.3647</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.8216</v>
+        <v>-3.4092</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.537</v>
+        <v>-2.9555</v>
       </c>
       <c r="G21" t="n">
         <v>-7.0841</v>
@@ -2092,13 +2092,13 @@
         <v>2.2234</v>
       </c>
       <c r="S21" t="n">
-        <v>2.2814</v>
+        <v>1.2753</v>
       </c>
       <c r="T21" t="n">
-        <v>1.6564</v>
+        <v>1.0689</v>
       </c>
       <c r="U21" t="n">
-        <v>0.625</v>
+        <v>0.2064</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-10.9095</v>
+        <v>-10.2567</v>
       </c>
       <c r="E22" t="n">
-        <v>5.794699999999999</v>
+        <v>5.794599999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>-16.7043</v>
+        <v>-16.0516</v>
       </c>
       <c r="G22" t="n">
         <v>-14.4434</v>
@@ -2170,13 +2170,13 @@
         <v>12.0437</v>
       </c>
       <c r="S22" t="n">
-        <v>4.1286</v>
+        <v>4.781499999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>3.6498</v>
+        <v>3.6499</v>
       </c>
       <c r="U22" t="n">
-        <v>0.4786</v>
+        <v>1.1314</v>
       </c>
       <c r="V22" t="n">
         <v>1.2583</v>
